--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-ballot</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:44:45+00:00</t>
+    <t>2024-03-25T10:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:59:40+00:00</t>
+    <t>2024-03-25T11:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T08:02:06+00:00</t>
+    <t>2024-05-23T12:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:05:52+00:00</t>
+    <t>2024-05-23T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:32:02+00:00</t>
+    <t>2024-05-23T14:35:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T14:35:00+00:00</t>
+    <t>2024-06-11T15:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:12+00:00</t>
+    <t>2024-06-11T15:33:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:34+00:00</t>
+    <t>2024-07-02T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(WORK))</t>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T11:39:28+00:00</t>
+    <t>2024-07-17T12:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:13:27+00:00</t>
+    <t>2024-07-17T14:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T14:21:13+00:00</t>
+    <t>2024-07-17T15:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:15:49+00:00</t>
+    <t>2024-07-17T15:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T07:11:02+00:00</t>
+    <t>2024-07-25T15:28:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:28:42+00:00</t>
+    <t>2024-07-25T15:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:29:18+00:00</t>
+    <t>2024-07-25T15:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:44:10+00:00</t>
+    <t>2024-08-01T13:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0-ballot</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-03T15:38:30+00:00</t>
+    <t>2024-09-04T07:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T07:28:39+00:00</t>
+    <t>2024-09-04T07:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T12:53:53+00:00</t>
+    <t>2024-10-28T08:07:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:07:18+00:00</t>
+    <t>2024-10-28T08:08:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:08:30+00:00</t>
+    <t>2024-10-29T10:42:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:05:50+00:00</t>
+    <t>2025-01-28T09:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:07:36+00:00</t>
+    <t>2025-02-04T08:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T08:51:44+00:00</t>
+    <t>2025-02-04T09:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:30:35+00:00</t>
+    <t>2025-02-19T13:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:47:59+00:00</t>
+    <t>2025-02-19T13:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:52:01+00:00</t>
+    <t>2025-02-19T13:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:53:58+00:00</t>
+    <t>2025-02-19T13:58:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:58:46+00:00</t>
+    <t>2025-02-19T14:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T14:07:54+00:00</t>
+    <t>2025-02-19T14:26:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:11:18+00:00</t>
+    <t>2025-05-20T13:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:27:17+00:00</t>
+    <t>2025-05-20T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:29:42+00:00</t>
+    <t>2025-05-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="85">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:48:39+00:00</t>
+    <t>2025-06-04T13:32:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -612,7 +612,9 @@
       <c r="C2" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -624,7 +626,9 @@
       <c r="C3" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -636,7 +640,9 @@
       <c r="C4" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>48</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
@@ -648,7 +654,9 @@
       <c r="C5" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>50</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
@@ -660,7 +668,9 @@
       <c r="C6" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>52</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
@@ -672,7 +682,9 @@
       <c r="C7" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>54</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
@@ -684,7 +696,9 @@
       <c r="C8" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>56</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
@@ -696,7 +710,9 @@
       <c r="C9" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>58</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
@@ -708,7 +724,9 @@
       <c r="C10" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>60</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
@@ -720,7 +738,9 @@
       <c r="C11" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>62</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
@@ -732,7 +752,9 @@
       <c r="C12" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="D12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>64</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
@@ -744,7 +766,9 @@
       <c r="C13" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="D13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>66</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
@@ -756,7 +780,9 @@
       <c r="C14" t="s" s="2">
         <v>68</v>
       </c>
-      <c r="D14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>68</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
@@ -768,7 +794,9 @@
       <c r="C15" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="D15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>70</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
@@ -780,7 +808,9 @@
       <c r="C16" t="s" s="2">
         <v>72</v>
       </c>
-      <c r="D16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>72</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
@@ -792,7 +822,9 @@
       <c r="C17" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="D17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>74</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
@@ -804,7 +836,9 @@
       <c r="C18" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="D18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>76</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
@@ -816,7 +850,9 @@
       <c r="C19" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="D19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
@@ -828,7 +864,9 @@
       <c r="C20" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="D20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>80</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
@@ -840,7 +878,9 @@
       <c r="C21" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="D21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>82</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
@@ -852,7 +892,9 @@
       <c r="C22" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="D22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>84</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T13:32:30+00:00</t>
+    <t>2025-06-24T17:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T17:01:22+00:00</t>
+    <t>2025-07-04T12:19:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T12:19:33+00:00</t>
+    <t>2025-07-08T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T13:28:39+00:00</t>
+    <t>2025-07-16T09:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T09:34:35+00:00</t>
+    <t>2025-07-30T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T14:55:53+00:00</t>
+    <t>2025-10-08T07:32:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:32:57+00:00</t>
+    <t>2025-10-08T12:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T12:04:30+00:00</t>
+    <t>2025-10-08T16:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:09:47+00:00</t>
+    <t>2026-03-25T10:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:11+00:00</t>
+    <t>2026-03-25T10:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:40+00:00</t>
+    <t>2026-03-25T10:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:25:13+00:00</t>
+    <t>2026-03-25T15:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:00:47+00:00</t>
+    <t>2026-03-31T09:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:16:18+00:00</t>
+    <t>2026-05-07T06:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:50:40+00:00</t>
+    <t>2026-05-27T14:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:53:55+00:00</t>
+    <t>2026-05-28T14:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:22:24+00:00</t>
+    <t>2026-06-12T14:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:04:24+00:00</t>
+    <t>2026-06-12T14:05:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:05:00+00:00</t>
+    <t>2026-06-12T14:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:35:23+00:00</t>
+    <t>2026-06-26T12:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:32:04+00:00</t>
+    <t>2026-06-29T09:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:30:52+00:00</t>
+    <t>2026-07-22T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:07+00:00</t>
+    <t>2026-07-27T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:02:31+00:00</t>
+    <t>2026-08-03T12:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:52:25+00:00</t>
+    <t>2026-08-04T12:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:22:31+00:00</t>
+    <t>2026-08-04T12:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-v2-0445.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:29:23+00:00</t>
+    <t>2026-08-10T16:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
